--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T09:28:26+00:00</t>
+    <t>2025-02-06T11:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T11:21:55+00:00</t>
+    <t>2025-02-06T12:00:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:00:33+00:00</t>
+    <t>2025-02-10T09:34:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T09:34:03+00:00</t>
+    <t>2025-02-10T11:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MOPEDTransferEncounter#Encounter</t>
+    <t>element:http://example.org/StructureDefinition/MopedTransferEncounter#Encounter</t>
   </si>
   <si>
     <t>ID</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-physischeAnwesenheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
